--- a/src/main/resources/plantillas/vacaciones.xlsx
+++ b/src/main/resources/plantillas/vacaciones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Exon\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\migracion\integra-backend\src\main\resources\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED788BE8-1CEB-4DE9-9C73-B5446D7C4559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCB3A04-A5C5-44CA-AC57-128FBD74D47A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EFEF002E-5400-4F52-A448-61427D5DB245}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <customWorkbookViews>
+    <customWorkbookView name="impresion" guid="{632161C1-85C1-46CA-992D-9AC5B90DC8D7}" maximized="1" xWindow="-8" yWindow="-8" windowWidth="1382" windowHeight="744" activeSheetId="1"/>
+  </customWorkbookViews>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,8 +41,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
   <si>
     <t>Reporte generado el 02-03-2026 13:24</t>
   </si>
@@ -50,9 +75,6 @@
     <t>UNIDAD ASOCIADA</t>
   </si>
   <si>
-    <t>VACACIONES DISPONIBLES</t>
-  </si>
-  <si>
     <t>PUESTO</t>
   </si>
   <si>
@@ -89,38 +111,94 @@
     <t>CLAVE</t>
   </si>
   <si>
-    <t>PABLO REYES LORENZO</t>
-  </si>
-  <si>
-    <t>75844 SALINA CRUZ 8</t>
-  </si>
-  <si>
-    <t>AUXILIAR ADMINISTRATIVO</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>ALEXIS ROSENDO RAMIREZ</t>
-  </si>
-  <si>
-    <t>VIRGINIA HERNANDEZ VIERA</t>
-  </si>
-  <si>
     <t>TOMADAS</t>
   </si>
   <si>
     <t>RESTANTES</t>
   </si>
   <si>
-    <t>VIGENTE</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>GESTIÓN DE VACACIONES</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>SALDOS VACACIONALES COMIALEX SA DE CV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Activo   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Reingreso</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,6 +249,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -193,7 +293,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color theme="1" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -201,31 +301,43 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -242,6 +354,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -561,438 +737,427 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58C5D58D-C8A0-4901-8D5D-DCEAE922B597}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="35.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="38.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="18" style="4" customWidth="1"/>
-    <col min="6" max="6" width="25.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="32.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="34.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15" style="3" customWidth="1"/>
-    <col min="10" max="10" width="16" style="5" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="18" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="3"/>
-    <col min="17" max="17" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="11.42578125" style="3"/>
+    <col min="1" max="1" width="8.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="38.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="32.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="34.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15" style="2" customWidth="1"/>
+    <col min="10" max="10" width="16" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="2"/>
+    <col min="17" max="17" width="13.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="1" spans="1:17" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="12"/>
+    </row>
+    <row r="2" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:17" s="6" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="7"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="8"/>
+      <c r="Q3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="10" t="s">
+      <c r="K4" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="10" t="s">
+      <c r="Q4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="O4" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="10" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>2064</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1">
-        <v>44774</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1">
-        <v>45505</v>
-      </c>
-      <c r="K5" s="1">
-        <v>45869</v>
-      </c>
-      <c r="L5" s="1">
-        <v>46235</v>
-      </c>
-      <c r="M5" s="2">
-        <v>16</v>
-      </c>
-      <c r="N5" s="2">
-        <v>10</v>
-      </c>
-      <c r="O5" s="2">
-        <v>6</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>2024</v>
-      </c>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <customSheetViews>
+    <customSheetView guid="{632161C1-85C1-46CA-992D-9AC5B90DC8D7}" showPageBreaks="1" fitToPage="1" view="pageLayout">
+      <selection activeCell="C13" sqref="C13"/>
+      <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+      <printOptions horizontalCentered="1"/>
+      <pageSetup scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+      <headerFooter>
+        <oddFooter>&amp;CPágina &amp;P</oddFooter>
+      </headerFooter>
+    </customSheetView>
+  </customSheetViews>
+  <mergeCells count="2">
     <mergeCell ref="J3:K3"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>
+  <pageSetup scale="39" fitToHeight="0" orientation="landscape" r:id="rId2"/>
+  <headerFooter>
+    <oddFooter>&amp;CPágina &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>